--- a/rosnedra_forecast/2026/rosnedra_page9.xlsx
+++ b/rosnedra_forecast/2026/rosnedra_page9.xlsx
@@ -416,12 +416,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -443,7 +443,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Извлекаемые запасы и природные ресурсы (с указанием категории) (ед.изм)</t>
+          <t>Извлекаемые запасы и прогнозные ресурсы</t>
         </is>
       </c>
     </row>
@@ -453,20 +453,19 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Северо-Салымский</t>
+          <t>Приразломный-3</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>нефть (геол./извл.):
-D1 - 10,274/3,082 млн т
-газ (геол./извл.):
-D1 - 0,681/0,681 млрд м3</t>
+          <t>нефть (извл.)
+Д1 - 4,267 млн.т
+Д2 - 1,658 млн.т</t>
         </is>
       </c>
     </row>
@@ -476,20 +475,23 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Западно-Угутский</t>
+          <t>Восточно-Айгульский</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>нефть (извл.):
-C1 - 5,712 млн т
-газ (извл.):
-C1 - 0,734 млрд м3</t>
+          <t>нефть (извл.)
+Д0 - 1,717 млн.т
+Д1 - 13,4 млн.т
+Д2 - 0,7 млн.т
+газ
+Д1 - 2,9 млрд.м3
+Д2 - 2,7 млрд.м3</t>
         </is>
       </c>
     </row>
@@ -499,20 +501,19 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Восточно-Угутский</t>
+          <t>Восточно-Высотный</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>нефть (извл.):
-C1 - 6,894 млн т
-газ (извл.):
-C1 - 0,885 млрд м3</t>
+          <t>нефть (извл.)
+Д1 - 5,4 млн.т
+Д2 - 0,1 млн.т</t>
         </is>
       </c>
     </row>
@@ -522,20 +523,21 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Южно-Угутский</t>
+          <t>Восточно-Заозерный</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>нефть (извл.):
-C1 - 4,336 млн т
-газ (извл.):
-C1 - 0,557 млрд м3</t>
+          <t>нефть (извл.)
+Д1 - 4,2 млн.т
+Д2 - 0,4 млн.т
+газ
+Д2 - 0,3 млрд.м3</t>
         </is>
       </c>
     </row>
@@ -545,20 +547,23 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Северо-Угутский</t>
+          <t>Западно-Токушинский</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>нефть (извл.):
-C1 - 7,148 млн т
-газ (извл.):
-C1 - 0,919 млрд м3</t>
+          <t>нефть (извл.)
+Д1 - 0,3 млн.т
+Д1 - 0,1 млн.т
+Д2 - 0,8 млн.т
+газ (извл.)
+Д1 - 5,1 млрд.м3
+Д2 - 0,6 млрд.м3</t>
         </is>
       </c>
     </row>
@@ -568,18 +573,20 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Чукотский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Верхне-Телекайский</t>
+          <t>Восточно-Толумский</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>золото рудное:
-C1 - 7,2 т</t>
+          <t>нефть (извл.)
+C1 - 0,156 млн.т
+C2 - 0,814 млн.т
+D0 - 0,919 млн.т</t>
         </is>
       </c>
     </row>
@@ -589,18 +596,20 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Чукотский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Нижне-Телекайский</t>
+          <t>Восточно-Саранпаульский</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>золото рудное:
-C1 - 5,8 т</t>
+          <t>нефть (извл.)
+Д1 - 0,74 млн.т
+газ
+Д2 - 2,05 млрд.м3</t>
         </is>
       </c>
     </row>
@@ -610,41 +619,26 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Чукотский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Южно-Телекайский</t>
+          <t>Казымский</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>золото рудное:
-C1 - 6,4 т</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>Ямало-Ненецкий автономный округ</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>Восточно-Тамбейский</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>газ (извл.):
-C1 - 145,8 млрд м3
-конденсат (извл.):
-C1 - 8,91 млн т</t>
+          <t>нефть (извл.)
+Д0 - 14,006 млн.т
+Д1 - 2,484 млн.т
+Д2 - 17,255 млн.т
+газ
+Д1 - 0,783 млрд.м3
+Д2 - 0,753 млрд.м3
+конденсат (извл.)
+Д1 - 0,023 млн.т
+Д2 - 0,210 млн.т</t>
         </is>
       </c>
     </row>
